--- a/excel-files/MANDALUYONG/HULO INTEGRATED SCHOOL.xlsx
+++ b/excel-files/MANDALUYONG/HULO INTEGRATED SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E94A0B7-BF8A-4206-99D2-612672B59442}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8219707C-63C9-430C-8868-29A32C53B710}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -754,6 +754,18 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -765,18 +777,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5467,8 +5467,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5487,7 +5487,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5504,38 +5504,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="42" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="43" t="s">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="44" t="s">
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5624,7 +5624,7 @@
       <c r="A3" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="41" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="32"/>
@@ -5709,7 +5709,7 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1"/>
@@ -6274,7 +6274,7 @@
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="1"/>
@@ -6840,7 +6840,7 @@
       <c r="A23" s="1">
         <v>3</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="42" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="1"/>
@@ -7751,7 +7751,7 @@
       <c r="A37" s="1">
         <v>4</v>
       </c>
-      <c r="B37" s="47" t="s">
+      <c r="B37" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C37" s="1"/>
@@ -8386,7 +8386,7 @@
       <c r="A47" s="1">
         <v>5</v>
       </c>
-      <c r="B47" s="47" t="s">
+      <c r="B47" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C47" s="1"/>
@@ -9021,7 +9021,7 @@
       <c r="A57" s="1">
         <v>6</v>
       </c>
-      <c r="B57" s="47" t="s">
+      <c r="B57" s="43" t="s">
         <v>17</v>
       </c>
       <c r="C57" s="1"/>
@@ -9656,7 +9656,7 @@
       <c r="A67" s="10">
         <v>7</v>
       </c>
-      <c r="B67" s="48" t="s">
+      <c r="B67" s="44" t="s">
         <v>17</v>
       </c>
       <c r="C67" s="10"/>
@@ -12265,7 +12265,7 @@
       <c r="A108" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B108" s="47" t="s">
+      <c r="B108" s="43" t="s">
         <v>31</v>
       </c>
       <c r="C108" s="1"/>
@@ -12334,7 +12334,7 @@
       <c r="A109" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B109" s="47" t="s">
+      <c r="B109" s="43" t="s">
         <v>32</v>
       </c>
       <c r="C109" s="1"/>
@@ -13466,186 +13466,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13665,8 +13485,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13688,7 +13508,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
@@ -13708,40 +13528,40 @@
     <col min="24" max="27" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="25.5" customHeight="1">
       <c r="B1" s="34"/>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="42" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="43" t="s">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="44" t="s">
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13826,7 +13646,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="36" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -22189,186 +22009,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22386,8 +22026,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/MANDALUYONG/HULO INTEGRATED SCHOOL.xlsx
+++ b/excel-files/MANDALUYONG/HULO INTEGRATED SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8219707C-63C9-430C-8868-29A32C53B710}"/>
+  <xr:revisionPtr revIDLastSave="417" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9804DCB5-4E7B-4647-99C9-B5394E4BE007}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="94">
   <si>
     <t>Grade Level</t>
   </si>
@@ -318,12 +318,15 @@
   <si>
     <t>Arts</t>
   </si>
+  <si>
+    <t>ESP</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,6 +438,12 @@
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="13">
@@ -640,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -778,6 +787,22 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3116,8 +3141,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
-  <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA142" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+  <autoFilter ref="A2:AA142" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
@@ -3502,7 +3527,7 @@
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="41.25" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -4102,16 +4127,22 @@
         <v>20</v>
       </c>
       <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="1">
+        <v>440</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4133,7 +4164,7 @@
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
-        <v>280</v>
+        <v>562</v>
       </c>
       <c r="E31" s="1">
         <v>2025</v>
@@ -4147,7 +4178,7 @@
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>280</v>
+        <v>562</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4245,7 +4276,7 @@
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
-        <v>280</v>
+        <v>562</v>
       </c>
       <c r="E36" s="1">
         <v>2025</v>
@@ -4259,7 +4290,7 @@
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>280</v>
+        <v>562</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4271,7 +4302,7 @@
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
-        <v>280</v>
+        <v>561</v>
       </c>
       <c r="E37" s="1">
         <v>2025</v>
@@ -4285,7 +4316,7 @@
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>280</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4296,16 +4327,22 @@
         <v>19</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="D38" s="1">
+        <v>282</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -9376,7 +9413,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9433,19 +9470,25 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W63" s="12"/>
-      <c r="X63" s="10"/>
-      <c r="Y63" s="12"/>
+      <c r="W63" s="12">
+        <v>138</v>
+      </c>
+      <c r="X63" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y63" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z63" s="12">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA63" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9502,19 +9545,25 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W64" s="12"/>
-      <c r="X64" s="10"/>
-      <c r="Y64" s="12"/>
+      <c r="W64" s="12">
+        <v>138</v>
+      </c>
+      <c r="X64" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y64" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z64" s="12">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA64" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9571,19 +9620,25 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W65" s="12"/>
-      <c r="X65" s="10"/>
-      <c r="Y65" s="12"/>
+      <c r="W65" s="12">
+        <v>138</v>
+      </c>
+      <c r="X65" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y65" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z65" s="12">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA65" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9640,16 +9695,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W66" s="12"/>
-      <c r="X66" s="10"/>
-      <c r="Y66" s="12"/>
+      <c r="W66" s="12">
+        <v>138</v>
+      </c>
+      <c r="X66" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y66" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z66" s="12">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA66" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:27" ht="36.75">
@@ -9709,19 +9770,25 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W67" s="12"/>
-      <c r="X67" s="10"/>
-      <c r="Y67" s="12"/>
+      <c r="W67" s="12">
+        <v>138</v>
+      </c>
+      <c r="X67" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y67" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z67" s="12">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA67" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9778,19 +9845,25 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W68" s="12"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="12"/>
+      <c r="W68" s="12">
+        <v>138</v>
+      </c>
+      <c r="X68" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y68" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z68" s="12">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA68" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9847,19 +9920,25 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W69" s="12"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="12"/>
+      <c r="W69" s="12">
+        <v>138</v>
+      </c>
+      <c r="X69" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y69" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z69" s="12">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA69" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9916,19 +9995,25 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W70" s="12"/>
-      <c r="X70" s="10"/>
-      <c r="Y70" s="12"/>
+      <c r="W70" s="12">
+        <v>138</v>
+      </c>
+      <c r="X70" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y70" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z70" s="12">
         <f t="shared" ref="Z70:Z127" si="20">IF((V70-W70)&lt;0,0,(V70-W70))</f>
         <v>0</v>
       </c>
       <c r="AA70" s="12">
         <f t="shared" ref="AA70:AA127" si="21">IF((W70-V70)&lt;0,0,(W70-V70))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9985,16 +10070,22 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W71" s="12"/>
-      <c r="X71" s="10"/>
-      <c r="Y71" s="12"/>
+      <c r="W71" s="12">
+        <v>138</v>
+      </c>
+      <c r="X71" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y71" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z71" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AA71" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
@@ -13471,8 +13562,8 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 W63:X71" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 Y14:Y110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13485,10 +13576,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X5:X12 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X63:X71" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 G103:G110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 Y14:Y110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13508,7 +13599,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB140"/>
+  <dimension ref="A1:AB142"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
@@ -14060,7 +14151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14406,7 +14497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14433,16 +14524,22 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="5"/>
+      <c r="K15" s="5">
+        <v>245</v>
+      </c>
+      <c r="L15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N15" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O15" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="P15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -14544,7 +14641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14571,16 +14668,22 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="5"/>
+      <c r="K17" s="5">
+        <v>245</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N17" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="P17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -16134,7 +16237,7 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16161,16 +16264,22 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="5"/>
+      <c r="K43" s="5">
+        <v>257</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N43" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="P43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -16272,7 +16381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16299,16 +16408,22 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="5"/>
+      <c r="K45" s="5">
+        <v>257</v>
+      </c>
+      <c r="L45" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N45" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="P45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -17278,7 +17393,6 @@
         <v>52</v>
       </c>
       <c r="V59" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
       <c r="W59" s="5">
@@ -17291,7 +17405,7 @@
         <v>9</v>
       </c>
       <c r="Z59" s="5">
-        <f t="shared" si="6"/>
+        <f>IF((V59-W59)&lt;0,0,(V59-W59))</f>
         <v>0</v>
       </c>
       <c r="AA59" s="5">
@@ -18273,11 +18387,11 @@
       <c r="R74" s="10"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
-        <f t="shared" ref="T74:T122" si="16">IF((P74-Q74)&lt;0,0,(P74-Q74))</f>
+        <f t="shared" ref="T74:T124" si="16">IF((P74-Q74)&lt;0,0,(P74-Q74))</f>
         <v>0</v>
       </c>
       <c r="U74" s="12">
-        <f t="shared" ref="U74:U122" si="17">IF((Q74-P74)&lt;0,0,(Q74-P74))</f>
+        <f t="shared" ref="U74:U124" si="17">IF((Q74-P74)&lt;0,0,(Q74-P74))</f>
         <v>0</v>
       </c>
       <c r="V74" s="12">
@@ -18288,11 +18402,11 @@
       <c r="X74" s="10"/>
       <c r="Y74" s="12"/>
       <c r="Z74" s="12">
-        <f t="shared" ref="Z74:Z122" si="18">IF((V74-W74)&lt;0,0,(V74-W74))</f>
+        <f t="shared" ref="Z74:Z124" si="18">IF((V74-W74)&lt;0,0,(V74-W74))</f>
         <v>0</v>
       </c>
       <c r="AA74" s="12">
-        <f t="shared" ref="AA74:AA122" si="19">IF((W74-V74)&lt;0,0,(W74-V74))</f>
+        <f t="shared" ref="AA74:AA124" si="19">IF((W74-V74)&lt;0,0,(W74-V74))</f>
         <v>0</v>
       </c>
     </row>
@@ -18535,11 +18649,11 @@
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
-        <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
+        <f t="shared" ref="N79:N124" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
         <v>0</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" ref="O74:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
+        <f t="shared" ref="O79:O124" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
         <v>0</v>
       </c>
       <c r="P79" s="12">
@@ -18865,11 +18979,11 @@
       <c r="F84" s="10"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
-        <f t="shared" ref="H84:H122" si="22">IF((D84-E84)&lt;0,0,(D84-E84))</f>
+        <f t="shared" ref="H84:H124" si="22">IF((D84-E84)&lt;0,0,(D84-E84))</f>
         <v>0</v>
       </c>
       <c r="I84" s="12">
-        <f t="shared" ref="I84:I122" si="23">IF((E84-D84)&lt;0,0,(E84-D84))</f>
+        <f t="shared" ref="I84:I124" si="23">IF((E84-D84)&lt;0,0,(E84-D84))</f>
         <v>0</v>
       </c>
       <c r="J84" s="12">
@@ -19372,31 +19486,43 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K92" s="12"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="12"/>
+      <c r="K92" s="12">
+        <v>472</v>
+      </c>
+      <c r="L92" s="10">
+        <v>2025</v>
+      </c>
+      <c r="M92" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="N92" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O92" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="P92" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q92" s="12"/>
-      <c r="R92" s="10"/>
-      <c r="S92" s="12"/>
+      <c r="Q92" s="12">
+        <v>59</v>
+      </c>
+      <c r="R92" s="10">
+        <v>2025</v>
+      </c>
+      <c r="S92" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="T92" s="12">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U92" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="V92" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -19453,16 +19579,22 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K93" s="12"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="12"/>
+      <c r="K93" s="12">
+        <v>590</v>
+      </c>
+      <c r="L93" s="10">
+        <v>2025</v>
+      </c>
+      <c r="M93" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="N93" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O93" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="P93" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -19663,7 +19795,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19705,108 +19837,126 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q96" s="12"/>
-      <c r="R96" s="10"/>
-      <c r="S96" s="12"/>
+      <c r="Q96" s="12">
+        <v>59</v>
+      </c>
+      <c r="R96" s="10">
+        <v>2026</v>
+      </c>
+      <c r="S96" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="T96" s="12">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U96" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="V96" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W96" s="12"/>
-      <c r="X96" s="10"/>
-      <c r="Y96" s="12"/>
+      <c r="W96" s="12">
+        <v>354</v>
+      </c>
+      <c r="X96" s="10">
+        <v>2026</v>
+      </c>
+      <c r="Y96" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z96" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA96" s="12">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
-      <c r="A97" s="37">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" ht="21">
+      <c r="A97" s="49">
         <v>9</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="C97" s="51"/>
+      <c r="D97" s="51">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="51"/>
+      <c r="F97" s="52"/>
+      <c r="G97" s="51"/>
+      <c r="H97" s="53">
+        <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
+        <v>0</v>
+      </c>
+      <c r="I97" s="53">
+        <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
+        <v>0</v>
+      </c>
+      <c r="J97" s="51">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K97" s="51"/>
+      <c r="L97" s="52"/>
+      <c r="M97" s="51"/>
+      <c r="N97" s="51"/>
+      <c r="O97" s="51"/>
+      <c r="P97" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="Q97" s="51">
+        <v>59</v>
+      </c>
+      <c r="R97" s="52">
+        <v>2026</v>
+      </c>
+      <c r="S97" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="T97" s="51">
+        <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
+        <v>0</v>
+      </c>
+      <c r="U97" s="51">
+        <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
+        <v>59</v>
+      </c>
+      <c r="V97" s="51">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W97" s="51">
+        <v>295</v>
+      </c>
+      <c r="X97" s="52">
+        <v>2026</v>
+      </c>
+      <c r="Y97" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z97" s="51">
+        <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
+        <v>0</v>
+      </c>
+      <c r="AA97" s="51">
+        <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" ht="19.149999999999999">
+      <c r="A98" s="37">
+        <v>9</v>
+      </c>
+      <c r="B98" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="12"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12">
-        <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
-        <v>0</v>
-      </c>
-      <c r="I97" s="12">
-        <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
-        <v>0</v>
-      </c>
-      <c r="J97" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="12"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="12"/>
-      <c r="N97" s="12">
-        <f t="shared" ref="N97:N101" si="26">IF((J97-K97)&lt;0,0,(J97-K97))</f>
-        <v>0</v>
-      </c>
-      <c r="O97" s="12">
-        <f t="shared" ref="O97:O101" si="27">IF((K97-J97)&lt;0,0,(K97-J97))</f>
-        <v>0</v>
-      </c>
-      <c r="P97" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q97" s="12"/>
-      <c r="R97" s="10"/>
-      <c r="S97" s="12"/>
-      <c r="T97" s="12">
-        <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
-        <v>0</v>
-      </c>
-      <c r="U97" s="12">
-        <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
-        <v>0</v>
-      </c>
-      <c r="V97" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W97" s="12"/>
-      <c r="X97" s="10"/>
-      <c r="Y97" s="12"/>
-      <c r="Z97" s="12">
-        <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
-        <v>0</v>
-      </c>
-      <c r="AA97" s="12">
-        <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="19.5">
-      <c r="A98" s="10">
-        <v>9</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19817,11 +19967,11 @@
       <c r="F98" s="10"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12">
-        <f t="shared" si="22"/>
+        <f>IF((D98-E98)&lt;0,0,(D98-E98))</f>
         <v>0</v>
       </c>
       <c r="I98" s="12">
-        <f t="shared" si="23"/>
+        <f>IF((E98-D98)&lt;0,0,(E98-D98))</f>
         <v>0</v>
       </c>
       <c r="J98" s="12">
@@ -19832,11 +19982,11 @@
       <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="N98:N102" si="26">IF((J98-K98)&lt;0,0,(J98-K98))</f>
         <v>0</v>
       </c>
       <c r="O98" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="O98:O102" si="27">IF((K98-J98)&lt;0,0,(K98-J98))</f>
         <v>0</v>
       </c>
       <c r="P98" s="12">
@@ -19847,41 +19997,35 @@
       <c r="R98" s="10"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
-        <f t="shared" si="16"/>
+        <f>IF((P98-Q98)&lt;0,0,(P98-Q98))</f>
         <v>0</v>
       </c>
       <c r="U98" s="12">
-        <f t="shared" si="17"/>
+        <f>IF((Q98-P98)&lt;0,0,(Q98-P98))</f>
         <v>0</v>
       </c>
       <c r="V98" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W98" s="12">
-        <v>59</v>
-      </c>
-      <c r="X98" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y98" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="W98" s="12"/>
+      <c r="X98" s="10"/>
+      <c r="Y98" s="12"/>
       <c r="Z98" s="12">
-        <f t="shared" si="18"/>
+        <f>IF((V98-W98)&lt;0,0,(V98-W98))</f>
         <v>0</v>
       </c>
       <c r="AA98" s="12">
-        <f t="shared" si="19"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+        <f>IF((W98-V98)&lt;0,0,(W98-V98))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -19933,24 +20077,30 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W99" s="12"/>
-      <c r="X99" s="10"/>
-      <c r="Y99" s="12"/>
+      <c r="W99" s="12">
+        <v>59</v>
+      </c>
+      <c r="X99" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y99" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="Z99" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA99" s="12">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100" spans="1:27" ht="19.149999999999999">
-      <c r="A100" s="37">
+      <c r="A100" s="10">
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19961,11 +20111,11 @@
       <c r="F100" s="10"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12">
-        <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I100" s="12">
-        <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J100" s="12">
@@ -19991,11 +20141,11 @@
       <c r="R100" s="10"/>
       <c r="S100" s="12"/>
       <c r="T100" s="12">
-        <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U100" s="12">
-        <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V100" s="12">
@@ -20006,20 +20156,20 @@
       <c r="X100" s="10"/>
       <c r="Y100" s="12"/>
       <c r="Z100" s="12">
-        <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA100" s="12">
-        <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:27" ht="19.5">
-      <c r="A101" s="10">
+      <c r="A101" s="37">
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20030,11 +20180,11 @@
       <c r="F101" s="10"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12">
-        <f t="shared" si="22"/>
+        <f>IF((D101-E101)&lt;0,0,(D101-E101))</f>
         <v>0</v>
       </c>
       <c r="I101" s="12">
-        <f t="shared" si="23"/>
+        <f>IF((E101-D101)&lt;0,0,(E101-D101))</f>
         <v>0</v>
       </c>
       <c r="J101" s="12">
@@ -20056,133 +20206,127 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q101" s="12"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="12"/>
+      <c r="Q101" s="12">
+        <v>59</v>
+      </c>
+      <c r="R101" s="10">
+        <v>2025</v>
+      </c>
+      <c r="S101" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="T101" s="12">
+        <f>IF((P101-Q101)&lt;0,0,(P101-Q101))</f>
+        <v>0</v>
+      </c>
+      <c r="U101" s="12">
+        <f>IF((Q101-P101)&lt;0,0,(Q101-P101))</f>
+        <v>59</v>
+      </c>
+      <c r="V101" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W101" s="12"/>
+      <c r="X101" s="10"/>
+      <c r="Y101" s="12"/>
+      <c r="Z101" s="12">
+        <f>IF((V101-W101)&lt;0,0,(V101-W101))</f>
+        <v>0</v>
+      </c>
+      <c r="AA101" s="12">
+        <f>IF((W101-V101)&lt;0,0,(W101-V101))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" ht="19.5">
+      <c r="A102" s="10">
+        <v>9</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C102" s="10"/>
+      <c r="D102" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E102" s="12"/>
+      <c r="F102" s="10"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="12">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I102" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J102" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K102" s="12"/>
+      <c r="L102" s="10"/>
+      <c r="M102" s="12"/>
+      <c r="N102" s="12">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="O102" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="P102" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="Q102" s="12">
+        <v>59</v>
+      </c>
+      <c r="R102" s="10">
+        <v>2025</v>
+      </c>
+      <c r="S102" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="T102" s="12">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="U101" s="12">
+      <c r="U102" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V101" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W101" s="12">
         <v>59</v>
       </c>
-      <c r="X101" s="10">
+      <c r="V102" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W102" s="12">
+        <v>59</v>
+      </c>
+      <c r="X102" s="10">
         <v>2025</v>
       </c>
-      <c r="Y101" s="12" t="s">
+      <c r="Y102" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Z101" s="12">
+      <c r="Z102" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AA101" s="12">
+      <c r="AA102" s="12">
         <f t="shared" si="19"/>
         <v>59</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.5">
-      <c r="A103" s="10">
-        <v>10</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C103" s="10"/>
-      <c r="D103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E103" s="12">
-        <v>42</v>
-      </c>
-      <c r="F103" s="10">
-        <v>2025</v>
-      </c>
-      <c r="G103" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H103" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="12">
-        <f t="shared" si="23"/>
-        <v>42</v>
-      </c>
-      <c r="J103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K103" s="12">
-        <v>48</v>
-      </c>
-      <c r="L103" s="10">
-        <v>2025</v>
-      </c>
-      <c r="M103" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="N103" s="12">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O103" s="12">
-        <f t="shared" si="21"/>
-        <v>48</v>
-      </c>
-      <c r="P103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q103" s="12"/>
-      <c r="R103" s="10"/>
-      <c r="S103" s="12"/>
-      <c r="T103" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U103" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V103" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W103" s="12">
-        <v>48</v>
-      </c>
-      <c r="X103" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y103" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z103" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA103" s="12">
-        <f t="shared" si="19"/>
-        <v>48</v>
-      </c>
-    </row>
+    <row r="103" spans="1:27" s="7" customFormat="1"/>
     <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20210,31 +20354,43 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K104" s="12"/>
-      <c r="L104" s="10"/>
-      <c r="M104" s="12"/>
+      <c r="K104" s="12">
+        <v>48</v>
+      </c>
+      <c r="L104" s="10">
+        <v>2025</v>
+      </c>
+      <c r="M104" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="N104" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O104" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="P104" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q104" s="12"/>
-      <c r="R104" s="10"/>
-      <c r="S104" s="12"/>
+      <c r="Q104" s="12">
+        <v>48</v>
+      </c>
+      <c r="R104" s="10">
+        <v>2026</v>
+      </c>
+      <c r="S104" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="T104" s="12">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U104" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V104" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -20263,7 +20419,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="12">
@@ -20291,22 +20447,16 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K105" s="12">
-        <v>48</v>
-      </c>
-      <c r="L105" s="10">
-        <v>2025</v>
-      </c>
-      <c r="M105" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="K105" s="12"/>
+      <c r="L105" s="10"/>
+      <c r="M105" s="12"/>
       <c r="N105" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O105" s="12">
         <f t="shared" si="21"/>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="P105" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -20350,53 +20500,71 @@
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="E106" s="12"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="12"/>
+      <c r="E106" s="12">
+        <v>42</v>
+      </c>
+      <c r="F106" s="10">
+        <v>2025</v>
+      </c>
+      <c r="G106" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="H106" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I106" s="12">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J106" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K106" s="12"/>
-      <c r="L106" s="10"/>
-      <c r="M106" s="12"/>
+      <c r="K106" s="12">
+        <v>48</v>
+      </c>
+      <c r="L106" s="10">
+        <v>2025</v>
+      </c>
+      <c r="M106" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="N106" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O106" s="12">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="P106" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q106" s="12"/>
-      <c r="R106" s="10"/>
-      <c r="S106" s="12"/>
+      <c r="Q106" s="12">
+        <v>124</v>
+      </c>
+      <c r="R106" s="10">
+        <v>2026</v>
+      </c>
+      <c r="S106" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="T106" s="12">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U106" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="V106" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -20425,7 +20593,7 @@
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -20500,7 +20668,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -20537,16 +20705,22 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q108" s="12"/>
-      <c r="R108" s="10"/>
-      <c r="S108" s="12"/>
+      <c r="Q108" s="12">
+        <v>48</v>
+      </c>
+      <c r="R108" s="10">
+        <v>2026</v>
+      </c>
+      <c r="S108" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="T108" s="12">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U108" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V108" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -20571,11 +20745,11 @@
       </c>
     </row>
     <row r="109" spans="1:27" ht="19.5">
-      <c r="A109" s="37">
+      <c r="A109" s="10">
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20586,11 +20760,11 @@
       <c r="F109" s="10"/>
       <c r="G109" s="12"/>
       <c r="H109" s="12">
-        <f>IF((D109-E109)&lt;0,0,(D109-E109))</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I109" s="12">
-        <f>IF((E109-D109)&lt;0,0,(E109-D109))</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J109" s="12">
@@ -20601,11 +20775,11 @@
       <c r="L109" s="10"/>
       <c r="M109" s="12"/>
       <c r="N109" s="12">
-        <f t="shared" ref="N109:N113" si="28">IF((J109-K109)&lt;0,0,(J109-K109))</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O109" s="12">
-        <f t="shared" ref="O109:O113" si="29">IF((K109-J109)&lt;0,0,(K109-J109))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="P109" s="12">
@@ -20616,11 +20790,11 @@
       <c r="R109" s="10"/>
       <c r="S109" s="12"/>
       <c r="T109" s="12">
-        <f>IF((P109-Q109)&lt;0,0,(P109-Q109))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U109" s="12">
-        <f>IF((Q109-P109)&lt;0,0,(Q109-P109))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V109" s="12">
@@ -20637,95 +20811,89 @@
         <v>9</v>
       </c>
       <c r="Z109" s="12">
-        <f>IF((V109-W109)&lt;0,0,(V109-W109))</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA109" s="12">
-        <f>IF((W109-V109)&lt;0,0,(W109-V109))</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="110" spans="1:27" ht="19.5">
-      <c r="A110" s="10">
-        <v>10</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C110" s="10"/>
-      <c r="D110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E110" s="12"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="12"/>
-      <c r="H110" s="12">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I110" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="12"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="12"/>
-      <c r="N110" s="12">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="O110" s="12">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="P110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q110" s="12"/>
-      <c r="R110" s="10"/>
-      <c r="S110" s="12"/>
-      <c r="T110" s="12">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U110" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V110" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W110" s="12">
-        <v>48</v>
-      </c>
-      <c r="X110" s="10">
-        <v>2025</v>
-      </c>
-      <c r="Y110" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z110" s="12">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA110" s="12">
         <f t="shared" si="19"/>
         <v>48</v>
       </c>
     </row>
+    <row r="110" spans="1:27" s="54" customFormat="1" ht="21">
+      <c r="A110" s="49">
+        <v>10</v>
+      </c>
+      <c r="B110" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="C110" s="51"/>
+      <c r="D110" s="51">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E110" s="51"/>
+      <c r="F110" s="52"/>
+      <c r="G110" s="51"/>
+      <c r="H110" s="53">
+        <f>IF((D110-E110)&lt;0,0,(D110-E110))</f>
+        <v>0</v>
+      </c>
+      <c r="I110" s="53">
+        <f>IF((E110-D110)&lt;0,0,(E110-D110))</f>
+        <v>0</v>
+      </c>
+      <c r="J110" s="51">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K110" s="51"/>
+      <c r="L110" s="52"/>
+      <c r="M110" s="51"/>
+      <c r="N110" s="51"/>
+      <c r="O110" s="51"/>
+      <c r="P110" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="51">
+        <v>48</v>
+      </c>
+      <c r="R110" s="52">
+        <v>2026</v>
+      </c>
+      <c r="S110" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="T110" s="51">
+        <f>IF((P110-Q110)&lt;0,0,(P110-Q110))</f>
+        <v>0</v>
+      </c>
+      <c r="U110" s="51">
+        <f>IF((Q110-P110)&lt;0,0,(Q110-P110))</f>
+        <v>48</v>
+      </c>
+      <c r="V110" s="51">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W110" s="51"/>
+      <c r="X110" s="52"/>
+      <c r="Y110" s="51"/>
+      <c r="Z110" s="51">
+        <f>IF((V110-W110)&lt;0,0,(V110-W110))</f>
+        <v>0</v>
+      </c>
+      <c r="AA110" s="51">
+        <f>IF((W110-V110)&lt;0,0,(W110-V110))</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="111" spans="1:27" ht="19.5">
-      <c r="A111" s="10">
+      <c r="A111" s="37">
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -20736,11 +20904,11 @@
       <c r="F111" s="10"/>
       <c r="G111" s="12"/>
       <c r="H111" s="12">
-        <f t="shared" si="22"/>
+        <f>IF((D111-E111)&lt;0,0,(D111-E111))</f>
         <v>0</v>
       </c>
       <c r="I111" s="12">
-        <f t="shared" si="23"/>
+        <f>IF((E111-D111)&lt;0,0,(E111-D111))</f>
         <v>0</v>
       </c>
       <c r="J111" s="12">
@@ -20751,27 +20919,32 @@
       <c r="L111" s="10"/>
       <c r="M111" s="12"/>
       <c r="N111" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="N111:N115" si="28">IF((J111-K111)&lt;0,0,(J111-K111))</f>
         <v>0</v>
       </c>
       <c r="O111" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="O111:O115" si="29">IF((K111-J111)&lt;0,0,(K111-J111))</f>
         <v>0</v>
       </c>
       <c r="P111" s="12">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q111" s="12"/>
-      <c r="R111" s="10"/>
-      <c r="S111" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q111" s="12">
+        <v>124</v>
+      </c>
+      <c r="R111" s="10">
+        <v>2026</v>
+      </c>
+      <c r="S111" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="T111" s="12">
-        <f t="shared" si="16"/>
+        <f>IF((P111-Q111)&lt;0,0,(P111-Q111))</f>
         <v>0</v>
       </c>
       <c r="U111" s="12">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>IF((Q111-P111)&lt;0,0,(Q111-P111))</f>
+        <v>124</v>
       </c>
       <c r="V111" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
@@ -20787,20 +20960,20 @@
         <v>9</v>
       </c>
       <c r="Z111" s="12">
-        <f t="shared" si="18"/>
+        <f>IF((V111-W111)&lt;0,0,(V111-W111))</f>
         <v>0</v>
       </c>
       <c r="AA111" s="12">
-        <f t="shared" si="19"/>
+        <f>IF((W111-V111)&lt;0,0,(W111-V111))</f>
         <v>48</v>
       </c>
     </row>
     <row r="112" spans="1:27" ht="19.5">
-      <c r="A112" s="37">
+      <c r="A112" s="10">
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20811,11 +20984,11 @@
       <c r="F112" s="10"/>
       <c r="G112" s="12"/>
       <c r="H112" s="12">
-        <f>IF((D112-E112)&lt;0,0,(D112-E112))</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I112" s="12">
-        <f>IF((E112-D112)&lt;0,0,(E112-D112))</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="J112" s="12">
@@ -20841,11 +21014,11 @@
       <c r="R112" s="10"/>
       <c r="S112" s="12"/>
       <c r="T112" s="12">
-        <f>IF((P112-Q112)&lt;0,0,(P112-Q112))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U112" s="12">
-        <f>IF((Q112-P112)&lt;0,0,(Q112-P112))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V112" s="12">
@@ -20862,11 +21035,11 @@
         <v>9</v>
       </c>
       <c r="Z112" s="12">
-        <f>IF((V112-W112)&lt;0,0,(V112-W112))</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AA112" s="12">
-        <f>IF((W112-V112)&lt;0,0,(W112-V112))</f>
+        <f t="shared" si="19"/>
         <v>48</v>
       </c>
     </row>
@@ -20875,7 +21048,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20945,151 +21118,169 @@
         <v>48</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
-      <c r="A115" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C115" s="1"/>
-      <c r="D115" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E115" s="5"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="5"/>
-      <c r="H115" s="5">
+    <row r="114" spans="1:28" ht="19.5">
+      <c r="A114" s="37">
+        <v>10</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C114" s="10"/>
+      <c r="D114" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E114" s="12"/>
+      <c r="F114" s="10"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="12">
+        <f>IF((D114-E114)&lt;0,0,(D114-E114))</f>
+        <v>0</v>
+      </c>
+      <c r="I114" s="12">
+        <f>IF((E114-D114)&lt;0,0,(E114-D114))</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K114" s="12"/>
+      <c r="L114" s="10"/>
+      <c r="M114" s="12"/>
+      <c r="N114" s="12">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="O114" s="12">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="P114" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="Q114" s="12"/>
+      <c r="R114" s="10"/>
+      <c r="S114" s="12"/>
+      <c r="T114" s="12">
+        <f>IF((P114-Q114)&lt;0,0,(P114-Q114))</f>
+        <v>0</v>
+      </c>
+      <c r="U114" s="12">
+        <f>IF((Q114-P114)&lt;0,0,(Q114-P114))</f>
+        <v>0</v>
+      </c>
+      <c r="V114" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W114" s="12">
+        <v>48</v>
+      </c>
+      <c r="X114" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y114" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z114" s="12">
+        <f>IF((V114-W114)&lt;0,0,(V114-W114))</f>
+        <v>0</v>
+      </c>
+      <c r="AA114" s="12">
+        <f>IF((W114-V114)&lt;0,0,(W114-V114))</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" ht="19.5">
+      <c r="A115" s="10">
+        <v>10</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C115" s="10"/>
+      <c r="D115" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E115" s="12"/>
+      <c r="F115" s="10"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I115" s="5">
+      <c r="I115" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="J115" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K115" s="5"/>
-      <c r="L115" s="1"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O115" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P115" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q115" s="5"/>
-      <c r="R115" s="1"/>
-      <c r="S115" s="5"/>
-      <c r="T115" s="5">
+      <c r="J115" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K115" s="12"/>
+      <c r="L115" s="10"/>
+      <c r="M115" s="12"/>
+      <c r="N115" s="12">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="O115" s="12">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="P115" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="Q115" s="12">
+        <v>48</v>
+      </c>
+      <c r="R115" s="10">
+        <v>2026</v>
+      </c>
+      <c r="S115" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="T115" s="12">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="U115" s="5">
+      <c r="U115" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V115" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W115" s="5"/>
-      <c r="X115" s="1"/>
-      <c r="Y115" s="5"/>
-      <c r="Z115" s="5">
+        <v>48</v>
+      </c>
+      <c r="V115" s="12">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W115" s="12">
+        <v>48</v>
+      </c>
+      <c r="X115" s="10">
+        <v>2025</v>
+      </c>
+      <c r="Y115" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z115" s="12">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AA115" s="5">
+      <c r="AA115" s="12">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
-      <c r="A116" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C116" s="1"/>
-      <c r="D116" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E116" s="5"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="I116" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="J116" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K116" s="5"/>
-      <c r="L116" s="1"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="O116" s="5">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P116" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q116" s="5"/>
-      <c r="R116" s="1"/>
-      <c r="S116" s="5"/>
-      <c r="T116" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U116" s="5">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="V116" s="5">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W116" s="5"/>
-      <c r="X116" s="1"/>
-      <c r="Y116" s="5"/>
-      <c r="Z116" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA116" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" s="7" customFormat="1"/>
+    <row r="117" spans="1:28" ht="38.450000000000003">
       <c r="A117" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -21158,7 +21349,7 @@
         <v>25</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21222,12 +21413,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="19.149999999999999">
       <c r="A119" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21296,7 +21487,7 @@
         <v>25</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21365,7 +21556,7 @@
         <v>25</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21429,12 +21620,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="19.149999999999999">
       <c r="A122" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -21498,67 +21689,145 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
-      <c r="A124" s="7"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
-      <c r="O124" s="7"/>
-      <c r="P124" s="7"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="7"/>
-      <c r="S124" s="7"/>
-      <c r="T124" s="7"/>
-      <c r="U124" s="7"/>
-      <c r="V124" s="7"/>
-      <c r="W124" s="7"/>
-      <c r="X124" s="7"/>
-      <c r="Y124" s="7"/>
-      <c r="Z124" s="7"/>
-      <c r="AA124" s="7"/>
-      <c r="AB124" s="7"/>
-    </row>
-    <row r="125" spans="1:28">
-      <c r="A125" s="7"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="7"/>
-      <c r="Q125" s="7"/>
-      <c r="R125" s="7"/>
-      <c r="S125" s="7"/>
-      <c r="T125" s="7"/>
-      <c r="U125" s="7"/>
-      <c r="V125" s="7"/>
-      <c r="W125" s="7"/>
-      <c r="X125" s="7"/>
-      <c r="Y125" s="7"/>
-      <c r="Z125" s="7"/>
-      <c r="AA125" s="7"/>
-      <c r="AB125" s="7"/>
-    </row>
+    <row r="123" spans="1:28" ht="38.450000000000003">
+      <c r="A123" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="D123" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E123" s="5"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I123" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J123" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K123" s="5"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O123" s="5">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P123" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="Q123" s="5"/>
+      <c r="R123" s="1"/>
+      <c r="S123" s="5"/>
+      <c r="T123" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U123" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V123" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W123" s="5"/>
+      <c r="X123" s="1"/>
+      <c r="Y123" s="5"/>
+      <c r="Z123" s="5">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AA123" s="5">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" ht="38.450000000000003">
+      <c r="A124" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E124" s="5"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I124" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="J124" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K124" s="5"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O124" s="5">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="P124" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="Q124" s="5"/>
+      <c r="R124" s="1"/>
+      <c r="S124" s="5"/>
+      <c r="T124" s="5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U124" s="5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V124" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W124" s="5"/>
+      <c r="X124" s="1"/>
+      <c r="Y124" s="5"/>
+      <c r="Z124" s="5">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AA124" s="5">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" s="7" customFormat="1"/>
     <row r="126" spans="1:28">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
@@ -22009,11 +22278,71 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
+    <row r="141" spans="1:28">
+      <c r="A141" s="7"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="7"/>
+      <c r="H141" s="7"/>
+      <c r="I141" s="7"/>
+      <c r="J141" s="7"/>
+      <c r="K141" s="7"/>
+      <c r="L141" s="7"/>
+      <c r="M141" s="7"/>
+      <c r="N141" s="7"/>
+      <c r="O141" s="7"/>
+      <c r="P141" s="7"/>
+      <c r="Q141" s="7"/>
+      <c r="R141" s="7"/>
+      <c r="S141" s="7"/>
+      <c r="T141" s="7"/>
+      <c r="U141" s="7"/>
+      <c r="V141" s="7"/>
+      <c r="W141" s="7"/>
+      <c r="X141" s="7"/>
+      <c r="Y141" s="7"/>
+      <c r="Z141" s="7"/>
+      <c r="AA141" s="7"/>
+      <c r="AB141" s="7"/>
+    </row>
+    <row r="142" spans="1:28">
+      <c r="A142" s="7"/>
+      <c r="B142" s="7"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="7"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="7"/>
+      <c r="K142" s="7"/>
+      <c r="L142" s="7"/>
+      <c r="M142" s="7"/>
+      <c r="N142" s="7"/>
+      <c r="O142" s="7"/>
+      <c r="P142" s="7"/>
+      <c r="Q142" s="7"/>
+      <c r="R142" s="7"/>
+      <c r="S142" s="7"/>
+      <c r="T142" s="7"/>
+      <c r="U142" s="7"/>
+      <c r="V142" s="7"/>
+      <c r="W142" s="7"/>
+      <c r="X142" s="7"/>
+      <c r="Y142" s="7"/>
+      <c r="Z142" s="7"/>
+      <c r="AA142" s="7"/>
+      <c r="AB142" s="7"/>
+    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
-    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
+    <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C117:C124 C104:C115 C91:C102" name="Textbooks"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F102 D117:F124 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X102 Z91:AA102 H91:L102 T104:X115 Z104:AA115 H104:L115 N117:R124 T117:X124 Z117:AA124 H117:L124 D104:F115 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N104:R115 N91:R102" name="LAS"/>
+    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y102 G91:G102 M91:M102 S91:S102 Y104:Y115 G104:G115 M104:M115 S104:S115 Y117:Y124 G117:G124 M117:M124 S117:S124" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -22023,10 +22352,10 @@
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S117:S124 Y117:Y124 G117:G124 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y102 S91:S102 M91:M102 G91:G102 G104:G115 Y104:Y115 S104:S115 M104:M115 M117:M124" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F117:F124 F104:F115 F91:F102 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L117:L124 L104:L115 L91:L102 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R117:R124 R104:R115 R91:R102 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X117:X124 X104:X115 X91:X102 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
